--- a/database/existing_staff_migration_template.xlsx
+++ b/database/existing_staff_migration_template.xlsx
@@ -8,43 +8,55 @@
   </bookViews>
   <sheets>
     <sheet name="Staff Import" sheetId="1" r:id="rId4"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Staff Import'!$A$1:$AG$1</definedName>
+  </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>department_code</t>
+  </si>
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>employment_date</t>
+  </si>
+  <si>
+    <t>contract_type</t>
+  </si>
+  <si>
+    <t>role_name</t>
+  </si>
+  <si>
+    <t>staff_type</t>
+  </si>
+  <si>
+    <t>staff_category</t>
+  </si>
+  <si>
+    <t>middle_name</t>
+  </si>
   <si>
     <t>staff_no</t>
   </si>
   <si>
-    <t>first_name</t>
-  </si>
-  <si>
-    <t>last_name</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>department_code</t>
-  </si>
-  <si>
-    <t>position</t>
-  </si>
-  <si>
-    <t>employment_date</t>
-  </si>
-  <si>
-    <t>contract_type</t>
-  </si>
-  <si>
-    <t>role_name</t>
+    <t>supervisor_staff_no</t>
   </si>
   <si>
     <t>gender</t>
@@ -56,12 +68,6 @@
     <t>marital_status</t>
   </si>
   <si>
-    <t>staff_type</t>
-  </si>
-  <si>
-    <t>staff_category</t>
-  </si>
-  <si>
     <t>kra_pin</t>
   </si>
   <si>
@@ -107,73 +113,73 @@
     <t>communication_phone</t>
   </si>
   <si>
-    <t>KWPS-001</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Wanjiku</t>
-  </si>
-  <si>
-    <t>jane.wanjiku@example.com</t>
-  </si>
-  <si>
-    <t>0712345678</t>
-  </si>
-  <si>
-    <t>ACA</t>
-  </si>
-  <si>
-    <t>Class Teacher</t>
-  </si>
-  <si>
-    <t>2024-01-08</t>
-  </si>
-  <si>
-    <t>permanent</t>
-  </si>
-  <si>
-    <t>female</t>
-  </si>
-  <si>
-    <t>1993-02-10</t>
-  </si>
-  <si>
-    <t>single</t>
-  </si>
-  <si>
-    <t>Teaching</t>
-  </si>
-  <si>
-    <t>Teacher</t>
-  </si>
-  <si>
-    <t>A123456789B</t>
-  </si>
-  <si>
-    <t>NSSF001</t>
-  </si>
-  <si>
-    <t>NHIF001</t>
-  </si>
-  <si>
-    <t>TSC001</t>
-  </si>
-  <si>
-    <t>Nairobi</t>
-  </si>
-  <si>
-    <t>KCB</t>
-  </si>
-  <si>
-    <t>08:00:00</t>
-  </si>
-  <si>
-    <t>17:00:00</t>
-  </si>
-  <si>
-    <t>yes</t>
+    <t>emergency_contact_name</t>
+  </si>
+  <si>
+    <t>emergency_contact_phone</t>
+  </si>
+  <si>
+    <t>Kingsway existing-staff import</t>
+  </si>
+  <si>
+    <t>Enter one staff member per row below the header. Do not rename, remove, or add columns.</t>
+  </si>
+  <si>
+    <t>Yellow headers are required. Other headers are optional unless made conditionally required below.</t>
+  </si>
+  <si>
+    <t>Dates</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>Times</t>
+  </si>
+  <si>
+    <t>HH:MM or HH:MM:SS; end time must be later than start time</t>
+  </si>
+  <si>
+    <t>Contract type</t>
+  </si>
+  <si>
+    <t>permanent, contract, or temporary</t>
+  </si>
+  <si>
+    <t>Payroll</t>
+  </si>
+  <si>
+    <t>Use yes/no. If yes, salary/basic_salary, bank_name, bank_account, kra_pin, nssf_no, and nhif_no are required.</t>
+  </si>
+  <si>
+    <t>Teaching roles</t>
+  </si>
+  <si>
+    <t>tsc_no is required and must be unique.</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
+  </si>
+  <si>
+    <t>Use the staff_no of an existing active supervisor.</t>
+  </si>
+  <si>
+    <t>Staff number</t>
+  </si>
+  <si>
+    <t>Leave blank to generate it automatically.</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Generated automatically from the login email; do not add a username column.</t>
+  </si>
+  <si>
+    <t>Import behavior</t>
+  </si>
+  <si>
+    <t>The entire batch must validate and commits atomically.</t>
   </si>
 </sst>
 </file>
@@ -181,7 +187,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -191,13 +197,37 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -212,8 +242,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,227 +548,289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:AG1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="20.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="20.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="19.852" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="16.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="25.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="19.852" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="23" max="23" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="25" max="25" width="20.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="26" max="26" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="27" max="27" width="29.279" bestFit="true" customWidth="true" style="0"/>
+    <col min="28" max="28" width="29.279" bestFit="true" customWidth="true" style="0"/>
+    <col min="29" max="29" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="30" max="30" width="25.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="31" max="31" width="25.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="32" max="32" width="29.279" bestFit="true" customWidth="true" style="0"/>
+    <col min="33" max="33" width="30.421" bestFit="true" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AG1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="23" max="23" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="25" max="25" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="26" max="26" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="27" max="27" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="28" max="28" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="29" max="29" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="30" max="30" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="24" customWidth="true" style="0"/>
+    <col min="2" max="2" width="110" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B1" s="4"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H2" t="s">
+      <c r="B4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I2" t="s">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="B5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="L2" t="s">
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="M2" t="s">
+      <c r="B6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="N2" t="s">
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="O2" t="s">
+      <c r="B7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="P2" t="s">
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="B8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="R2" t="s">
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="S2" t="s">
+      <c r="B9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="T2" t="s">
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="U2" t="s">
+      <c r="B10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="V2">
-        <v>1234567890</v>
-      </c>
-      <c r="W2">
-        <v>45000</v>
-      </c>
-      <c r="X2" t="s">
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="B11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Z2">
-        <v>15</v>
-      </c>
-      <c r="AA2" t="s">
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AB2">
-        <v>45000</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>34</v>
-      </c>
+      <c r="B12" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
